--- a/data/youth-unemployment.xlsx
+++ b/data/youth-unemployment.xlsx
@@ -8,20 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Klymchuk Dmytriy\Documents\ChatGPT\Пост в LinkedIn\youth-unemployment2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40ACB5E-DFAB-4CC7-A489-966A70F2D8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D40047-4511-44CA-B32B-AC7C74A3288F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Table" sheetId="2" r:id="rId1"/>
-    <sheet name="Data" sheetId="1" r:id="rId2"/>
+    <sheet name="Data" sheetId="2" r:id="rId1"/>
+    <sheet name="PivotSheet" sheetId="5" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="YouthUnemployment">YouthUnemployment3[]</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId3"/>
+  </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>Region</t>
   </si>
@@ -50,25 +56,10 @@
     <t>Northern, Southern and Western Europe</t>
   </si>
   <si>
-    <t>Source: ILO, Global Employment Trends for Youth 2026</t>
+    <t>Row Labels</t>
   </si>
   <si>
-    <t>https://www.ilo.org/resource/news/youth-unemployment-rises-young-people-face-harder-road-decent-work</t>
-  </si>
-  <si>
-    <t>Published: 11 August 2026. Estimates refer to 2025.</t>
-  </si>
-  <si>
-    <t>Rate denominator: labour force aged 15–24, not all young people.</t>
-  </si>
-  <si>
-    <t>Blank counts are unavailable in the cited release, not zero. World count is rounded.</t>
-  </si>
-  <si>
-    <t>World overlaps the regional rows. Do not sum rates or combine World with regions.</t>
-  </si>
-  <si>
-    <t>Power BI: import YouthUnemployment. Use Region and UnemploymentRate; format the rate as Percentage.</t>
+    <t>Sum of UnemploymentRate</t>
   </si>
 </sst>
 </file>
@@ -78,7 +69,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -92,11 +83,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF536573"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -125,14 +111,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -150,6 +140,1120 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[youth-unemployment.xlsx]PivotSheet!PivotTable3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Unemployment Rate for </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Youth</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> in 2025</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotSheet!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotSheet!$A$2:$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Northern, Southern and Western Europe</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Northern America</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>World</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotSheet!$B$2:$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.124</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A590-4AB6-A078-562CACC06C89}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="1336661935"/>
+        <c:axId val="1210922063"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1336661935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1210922063"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1210922063"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1336661935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E5AE3DD-4953-A6B7-E0A2-86EE21070A00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Klymchuk Dmytriy" refreshedDate="46275.576124421299" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{D8C35D47-3E17-4DFF-937D-C31FFD2FEF6C}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="YouthUnemployment3"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="3">
+        <s v="World"/>
+        <s v="Northern America"/>
+        <s v="Northern, Southern and Western Europe"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Year" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2025" maxValue="2025"/>
+    </cacheField>
+    <cacheField name="AgeGroup" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="UnemploymentRate" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.8000000000000004E-2" maxValue="0.15"/>
+    </cacheField>
+    <cacheField name="UnemployedPeople" numFmtId="3">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="67000000" maxValue="67000000"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="3">
+  <r>
+    <x v="0"/>
+    <n v="2025"/>
+    <s v="15–24"/>
+    <n v="0.124"/>
+    <n v="67000000"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2025"/>
+    <s v="15–24"/>
+    <n v="9.8000000000000004E-2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2025"/>
+    <s v="15–24"/>
+    <n v="0.15"/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A7A36ED5-12B0-400A-9772-959C5A80C6C3}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A1:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of UnemploymentRate" fld="3" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0ABA1B77-1DE6-4F48-A26D-BE178FA8E8C4}" name="YouthUnemployment3" displayName="YouthUnemployment3" ref="A1:E4" totalsRowShown="0">
   <tableColumns count="5">
@@ -158,19 +1262,6 @@
     <tableColumn id="3" xr3:uid="{71426201-63C7-459E-83F7-86F407C27F3B}" name="AgeGroup"/>
     <tableColumn id="4" xr3:uid="{3AA21A90-C9BF-47A9-96DE-9E156890FDA8}" name="UnemploymentRate"/>
     <tableColumn id="5" xr3:uid="{7770E8B3-A692-491A-9659-76092314CE71}" name="UnemployedPeople"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="YouthUnemployment" displayName="YouthUnemployment" ref="A1:E4" totalsRowShown="0">
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Region"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Year"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="AgeGroup"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="UnemploymentRate"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="UnemployedPeople"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -375,6 +1466,7 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="33.6875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.6875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -451,146 +1543,48 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038E624B-D010-49A4-9B84-47FC5C3D317D}">
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="53" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="5" width="25" customWidth="1"/>
+    <col min="1" max="1" width="33.6875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
+    <row r="1" spans="1:2">
+      <c r="A1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="8">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
-        <v>2025</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="B4" s="8">
         <v>0.124</v>
       </c>
-      <c r="E2" s="5">
-        <v>67000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2025</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4">
-        <v>9.8000000000000004E-2</v>
-      </c>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2025</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:5" ht="24" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" ht="24" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>